--- a/data_extactor/batch/251_300.xlsx
+++ b/data_extactor/batch/251_300.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45DF7E63-AE50-41E6-B71E-C722458C945F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B760C62-3C31-4433-A95E-37D6A4947B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="541">
   <si>
     <t>19-3092.00</t>
   </si>
@@ -1489,6 +1489,165 @@
   </si>
   <si>
     <t>Act as advisers to student organizations. | Advise students on academic and vocational curricula and career issues. | Collaborate with colleagues to address teaching and research issues. | Collaborate with members of the business community to improve programs, to develop new programs, and to provide student access to learning opportunities, such as internships. | Compile bibliographies of specialized materials for outside reading assignments. | Compile, administer, and grade examinations, or assign this work to others. | Conduct research in a particular field of knowledge and publish findings in professional journals, books, or electronic media. | Develop and maintain course Web sites. | Evaluate and grade students' class work, assignments, and papers. | Initiate, facilitate, and moderate classroom discussions. | Keep abreast of developments in the field by reading current literature, talking with colleagues, and participating in professional organizations and conferences. | Maintain regularly scheduled office hours to advise and assist students. | Maintain student attendance records, grades, and other required records. | Mentor new faculty. | Participate in campus and community events. | Participate in student recruitment, registration, and placement activities. | Perform administrative duties, such as serving as department head. | Plan, evaluate, and revise curricula, course content, and course materials and methods of instruction. | Prepare and deliver lectures to undergraduate or graduate students on topics such as financial accounting, principles of marketing, and operations management. | Prepare course materials, such as syllabi, homework assignments, and handouts. | Provide professional consulting services to government or industry. | Select and obtain materials and supplies, such as textbooks. | Serve on academic or administrative committees that deal with institutional policies, departmental matters, and academic issues. | Supervise undergraduate or graduate teaching, internship, and research work. | Write grant proposals to procure external research funding.</t>
+  </si>
+  <si>
+    <t>Foreign Policy Analyst | Government Affairs Analyst | Legislative Analyst | Policy Analyst | Political Analyst | Political Researcher | Political Scientist | Public Policy Analyst | Research Fellow | International Relations Analyst</t>
+  </si>
+  <si>
+    <t>Behavioral Scientist | Criminologist | Demographer | Ethnographer | Linguist | Policy Analyst | Public Opinion Analyst | Research Associate | Social Research Scientist | Social Scientist</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Structured query language SQL | Python | R | SAS | IBM SPSS Statistics | Tableau | Microsoft Power BI | Minitab | The MathWorks MATLAB | Oracle Database | Microsoft Access | Database software | Microsoft Word | Email software | Microsoft PowerPoint</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Active Listening | Speaking | Writing | Monitoring | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Sociology and Anthropology | English Language | Mathematics | Psychology | History and Archeology | Geography | Law and Government | Education and Training | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization | Mathematical Reasoning | Number Facility | Perceptual Speed | Flexibility of Closure</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Public Speaking</t>
+  </si>
+  <si>
+    <t>Sociologists | Anthropologists and Archeologists | Geographers | Historians | Political Scientists | Economists | Environmental Economists | Survey Researchers | Urban and Regional Planners | Transportation Planners | Social Science Research Assistants | Market Research Analysts and Marketing Specialists | Clinical and Counseling Psychologists | Industrial-Organizational Psychologists | Sociology Teachers, Postsecondary | Political Science Teachers, Postsecondary | Area, Ethnic, and Cultural Studies Teachers, Postsecondary | Statisticians | Management Analysts | Health Education Specialists</t>
+  </si>
+  <si>
+    <t>Conduct social science research in specialties not classified separately. | Design studies, surveys, and sampling strategies to investigate social questions. | Collect data through interviews, observation, surveys, and archival research. | Analyze quantitative and qualitative data to identify patterns and relationships. | Prepare research reports, policy briefs, and scholarly publications. | Advise government agencies and organizations on social policy and program design. | Evaluate the effectiveness of programs, interventions, and public policies. | Present findings to academic, governmental, and public audiences. | Review literature and theoretical frameworks relevant to research questions. | Ensure research complies with ethical standards for human subjects. | Develop and maintain databases, codebooks, and research documentation. | Supervise research assistants and coordinate data collection activities. | Prepare grant proposals and manage research project budgets. | Collaborate with researchers across disciplines and institutions.</t>
+  </si>
+  <si>
+    <t>Field Hydrologic Technician | Hydrographer | Hydrologic Aide | Hydrologic Technician | Hydrology Technician | Stream Gauging Technician | Water Quality Technician | Water Resources Technician | Watershed Technician | Groundwater Technician</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Monitoring | Active Listening | Speaking | Mathematics | Active Learning</t>
+  </si>
+  <si>
+    <t>Geography | Mathematics | Chemistry | English Language | Computers and Electronics | Engineering and Technology | Biology | Physics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Near Vision | Visualization | Arm-Hand Steadiness | Finger Dexterity | Manual Dexterity | Control Precision | Multilimb Coordination | Selective Attention | Category Flexibility | Mathematical Reasoning | Far Vision</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Outdoors, Under Cover | Exposed to Very Hot or Cold Temperatures | In an Open Vehicle or Operating Equipment | Spend Time Climbing Ladders, Scaffolds, or Poles | Exposed to High Places | Spend Time Kneeling, Crouching, Stooping, or Crawling | Spend Time Keeping or Regaining Balance | Face-to-Face Discussions with Individuals and Within Teams | E-Mail | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Indoors, Environmentally Controlled | Freedom to Make Decisions | Contact With Others | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Contaminants | Telephone Conversations</t>
+  </si>
+  <si>
+    <t>Analytical Technician | Field Technician | Laboratory Assistant | Laboratory Technician | Research Assistant | Research Technician | Sample Technician | Science Technician | Testing Technician | Lab Aide</t>
+  </si>
+  <si>
+    <t>Laboratory information management system LIMS | Microsoft Excel | Microsoft Word | IBM SPSS Statistics | SAS | R | Python | Database software | Email software | Microsoft PowerPoint | Minitab | Web browser software</t>
+  </si>
+  <si>
+    <t>Chemistry | Biology | Mathematics | English Language | Computers and Electronics | Engineering and Technology | Physics</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Hazardous Conditions | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Consequence of Error | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Biological Technicians | Chemical Technicians | Agricultural Technicians | Food Science Technicians | Environmental Science and Protection Technicians, Including Health | Geological Technicians, Except Hydrologic Technicians | Hydrologic Technicians | Nuclear Technicians | Nuclear Monitoring Technicians | Forensic Science Technicians | Forest and Conservation Technicians | Social Science Research Assistants | Quality Control Analysts | Remote Sensing Technicians | Precision Agriculture Technicians | Occupational Health and Safety Technicians | Occupational Health and Safety Specialists | Calibration Technologists and Technicians | Biologists | Chemists</t>
+  </si>
+  <si>
+    <t>Provide technical support in science specialties not classified separately. | Set up, calibrate, and operate laboratory and field instruments. | Collect, label, log, and prepare samples for analysis. | Perform standardized tests and analyses following written protocols. | Record measurements, observations, and test results accurately. | Compile data into tables, charts, and preliminary summary reports. | Clean, sterilize, and maintain laboratory equipment and work areas. | Monitor inventory of reagents, supplies, and consumables and place orders. | Troubleshoot instrument malfunctions and arrange servicing or repair. | Follow safety procedures for handling chemical, biological, and radiological materials. | Maintain quality control records, calibration logs, and chain-of-custody documentation. | Assist scientists in setting up experiments and field studies. | Dispose of hazardous waste according to established regulations. | Train new technicians on equipment operation and laboratory procedures.</t>
+  </si>
+  <si>
+    <t>Addiction Counselor | Behavioral Counselor | Career Counselor | Crisis Counselor | Family Counselor | Grief Counselor | Guidance Counselor | Peer Support Counselor | Youth Counselor | Wellness Counselor</t>
+  </si>
+  <si>
+    <t>Electronic medical record EMR software | Medical procedure coding software | Microsoft Excel | Microsoft Word | Email software | Database software | Scheduling software | Microsoft Outlook | Web browser software | Microsoft Office software | Microsoft PowerPoint</t>
+  </si>
+  <si>
+    <t>Therapy and Counseling | Psychology | English Language | Customer and Personal Service | Sociology and Anthropology | Education and Training | Law and Government | Administration and Management</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Conflict Situations | Dealing With Unpleasant, Angry, or Discourteous People | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Substance Abuse and Behavioral Disorder Counselors | Educational, Guidance, and Career Counselors and Advisors | Marriage and Family Therapists | Mental Health Counselors | Rehabilitation Counselors | Child, Family, and School Social Workers | Healthcare Social Workers | Mental Health and Substance Abuse Social Workers | Social Workers, All Other | Health Education Specialists | Probation Officers and Correctional Treatment Specialists | Social and Human Service Assistants | Community Health Workers | Community and Social Service Specialists, All Other | Clergy | Clinical and Counseling Psychologists | School Psychologists | Social Work Teachers, Postsecondary | Social and Community Service Managers | Recreational Therapists</t>
+  </si>
+  <si>
+    <t>Provide counseling services in specialties not classified separately. | Interview clients to assess needs, circumstances, and personal history. | Develop individualized treatment, service, or action plans with clients. | Conduct individual, group, and family counseling sessions. | Evaluate client progress and modify counseling approaches as needed. | Refer clients to community resources, specialists, and support services. | Maintain confidential case records, session notes, and progress documentation. | Educate clients and families about available options and coping strategies. | Respond to crisis situations and arrange emergency intervention when required. | Coordinate services with schools, employers, courts, and healthcare providers. | Facilitate workshops and support groups on relevant topics. | Adhere to professional ethics, confidentiality, and licensing requirements. | Prepare reports for agencies, courts, and funding organizations. | Participate in supervision, case conferences, and continuing education.</t>
+  </si>
+  <si>
+    <t>Case Manager | Clinical Social Worker | Community Social Worker | Geriatric Social Worker | Hospice Social Worker | Medical Social Worker | Public Health Social Worker | Social Services Coordinator | Social Worker | Youth Social Worker</t>
+  </si>
+  <si>
+    <t>Electronic medical record EMR software | Medical procedure coding software | Microsoft Excel | Microsoft Word | Email software | Database software | Scheduling software | Microsoft Outlook | Web browser software | Microsoft Office software</t>
+  </si>
+  <si>
+    <t>Therapy and Counseling | Psychology | Customer and Personal Service | English Language | Sociology and Anthropology | Law and Government | Education and Training | Administration and Management</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Conflict Situations | Physical Proximity | Dealing With Unpleasant, Angry, or Discourteous People</t>
+  </si>
+  <si>
+    <t>Child, Family, and School Social Workers | Healthcare Social Workers | Mental Health and Substance Abuse Social Workers | Counselors, All Other | Substance Abuse and Behavioral Disorder Counselors | Mental Health Counselors | Marriage and Family Therapists | Rehabilitation Counselors | Educational, Guidance, and Career Counselors and Advisors | Social and Human Service Assistants | Community Health Workers | Health Education Specialists | Community and Social Service Specialists, All Other | Probation Officers and Correctional Treatment Specialists | Social and Community Service Managers | Clinical and Counseling Psychologists | School Psychologists | Social Work Teachers, Postsecondary | Medical and Health Services Managers | Clergy</t>
+  </si>
+  <si>
+    <t>Provide social work services in specialties not classified separately. | Assess client needs, strengths, resources, and risk factors. | Develop, implement, and monitor individualized service plans. | Counsel individuals, families, and groups facing social or health difficulties. | Connect clients with housing, healthcare, financial, and legal resources. | Advocate on behalf of clients with agencies, providers, and institutions. | Investigate and respond to reports of abuse, neglect, or endangerment. | Maintain accurate case files, service records, and required documentation. | Coordinate interdisciplinary care with medical, educational, and legal professionals. | Prepare assessments and reports for courts, agencies, and funding bodies. | Provide crisis intervention and arrange emergency placements or services. | Educate clients and communities about available programs and entitlements. | Comply with professional ethics, confidentiality, and licensing standards. | Participate in case reviews, supervision, and professional development.</t>
+  </si>
+  <si>
+    <t>Case Aide | Community Outreach Specialist | Community Service Coordinator | Family Services Specialist | Human Services Specialist | Outreach Coordinator | Program Coordinator | Social Services Specialist | Victim Advocate | Youth Program Specialist</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | Microsoft Office software | Email software | Microsoft Access | Microsoft SharePoint | Web browser software | Database software | Google Docs | Calendar management software | Spreadsheet programs | Adobe Acrobat | Scheduling software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Critical Thinking | Monitoring | Writing</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Therapy and Counseling | Psychology | English Language | Sociology and Anthropology | Education and Training | Law and Government | Administration and Management</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Conflict Situations | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Social and Human Service Assistants | Community Health Workers | Health Education Specialists | Child, Family, and School Social Workers | Healthcare Social Workers | Mental Health and Substance Abuse Social Workers | Social Workers, All Other | Counselors, All Other | Substance Abuse and Behavioral Disorder Counselors | Mental Health Counselors | Rehabilitation Counselors | Educational, Guidance, and Career Counselors and Advisors | Probation Officers and Correctional Treatment Specialists | Social and Community Service Managers | Clergy | Directors, Religious Activities and Education | Fundraisers | Meeting, Convention, and Event Planners | Training and Development Specialists | Marriage and Family Therapists</t>
+  </si>
+  <si>
+    <t>Provide community and social service support in roles not classified separately. | Interview clients to determine eligibility for programs and services. | Assist clients in completing applications and obtaining required documentation. | Coordinate delivery of services among agencies, volunteers, and providers. | Conduct outreach to inform communities about available programs. | Organize and facilitate workshops, support groups, and community events. | Monitor client participation and progress toward program goals. | Maintain case records, service logs, and program statistics. | Prepare reports for supervisors, funders, and regulatory agencies. | Recruit, train, and supervise volunteers and program aides. | Advocate for clients in accessing benefits, housing, and healthcare. | Assist with crisis response and referral to emergency services. | Assemble and distribute educational materials and resource directories. | Support grant applications and program evaluation activities.</t>
+  </si>
+  <si>
+    <t>Chaplain Assistant | Church Administrator | Congregational Worker | Lay Minister | Missionary | Pastoral Associate | Religious Education Coordinator | Religious Program Specialist | Spiritual Care Coordinator | Youth Minister</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | Microsoft Office software | Email software | Microsoft Access | Microsoft SharePoint | Web browser software | Database software | Google Docs | Calendar management software | Spreadsheet programs | Adobe Acrobat | Graphic presentation software</t>
+  </si>
+  <si>
+    <t>Philosophy and Theology | English Language | Customer and Personal Service | Education and Training | Psychology | Sociology and Anthropology | Therapy and Counseling | Administration and Management</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Public Speaking | Physical Proximity | Conflict Situations</t>
+  </si>
+  <si>
+    <t>Clergy | Directors, Religious Activities and Education | Community and Social Service Specialists, All Other | Social and Human Service Assistants | Community Health Workers | Health Education Specialists | Child, Family, and School Social Workers | Social Workers, All Other | Counselors, All Other | Marriage and Family Therapists | Mental Health Counselors | Substance Abuse and Behavioral Disorder Counselors | Rehabilitation Counselors | Educational, Guidance, and Career Counselors and Advisors | Probation Officers and Correctional Treatment Specialists | Healthcare Social Workers | Mental Health and Substance Abuse Social Workers | Social and Community Service Managers | Philosophy and Religion Teachers, Postsecondary | Self-Enrichment Teachers</t>
+  </si>
+  <si>
+    <t>Perform religious and spiritual support duties not classified separately. | Assist clergy in conducting worship services, ceremonies, and observances. | Plan and lead religious education classes and study programs. | Provide spiritual support and comfort to individuals and families. | Organize outreach, mission, and community service activities. | Coordinate volunteers, committees, and congregational programs. | Prepare educational materials, bulletins, and program schedules. | Visit members in homes, hospitals, and care facilities. | Counsel individuals on personal, family, and spiritual concerns. | Maintain membership records, attendance data, and program documentation. | Assist with fundraising, stewardship, and budget administration. | Coordinate use of facilities for services, meetings, and events. | Refer individuals to professional counseling and social services when appropriate. | Participate in interfaith and community partnership activities.</t>
+  </si>
+  <si>
+    <t>Compliance Assistant | Contract Administrator | Court Clerk | Docket Clerk | Legal Analyst | Legal Assistant | Legal Research Assistant | Litigation Support Specialist | Patent Agent | Legal Support Specialist</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | Microsoft Office software | Email software | Microsoft Access | Microsoft SharePoint | Web browser software | Database software | Google Docs | Calendar management software | Spreadsheet programs | Adobe Acrobat | Microsoft Project</t>
+  </si>
+  <si>
+    <t>Law and Government | English Language | Administration and Management | Computers and Electronics | Customer and Personal Service | Economics and Accounting | Communications and Media</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Paralegals and Legal Assistants | Title Examiners, Abstractors, and Searchers | Judicial Law Clerks | Lawyers | Arbitrators, Mediators, and Conciliators | Administrative Law Judges, Adjudicators, and Hearing Officers | Judges, Magistrate Judges, and Magistrates | Court Reporters and Simultaneous Captioners | Compliance Officers | Regulatory Affairs Specialists | Claims Adjusters, Examiners, and Investigators | Human Resources Specialists | Legal Secretaries and Administrative Assistants | Executive Secretaries and Executive Administrative Assistants | Document Management Specialists | Management Analysts | Law Teachers, Postsecondary | Fraud Examiners, Investigators and Analysts | Insurance Underwriters | Financial Examiners</t>
+  </si>
+  <si>
+    <t>Provide legal support services in roles not classified separately. | Research statutes, regulations, case law, and legal precedents. | Draft, review, and proofread legal documents, correspondence, and filings. | Organize and maintain case files, exhibits, and document databases. | Track filing deadlines, court dates, and procedural requirements. | File documents with courts and regulatory agencies according to procedure. | Summarize depositions, contracts, and discovery materials for attorneys. | Coordinate with clients, witnesses, and opposing counsel to schedule proceedings. | Administer contracts and monitor compliance with terms and obligations. | Verify the accuracy and completeness of legal records and title documents. | Prepare indexes, chronologies, and evidence summaries for litigation. | Maintain confidentiality of privileged and sensitive information. | Assist with billing, timekeeping, and client account administration. | Support electronic discovery collection, review, and production activities.</t>
   </si>
 </sst>
 </file>
@@ -1886,6 +2045,9 @@
       <c r="B3" t="s">
         <v>23</v>
       </c>
+      <c r="C3" t="s">
+        <v>488</v>
+      </c>
       <c r="D3" t="s">
         <v>24</v>
       </c>
@@ -1918,8 +2080,32 @@
       <c r="B4" t="s">
         <v>33</v>
       </c>
+      <c r="C4" t="s">
+        <v>489</v>
+      </c>
+      <c r="D4" t="s">
+        <v>490</v>
+      </c>
+      <c r="E4" t="s">
+        <v>491</v>
+      </c>
+      <c r="F4" t="s">
+        <v>492</v>
+      </c>
+      <c r="G4" t="s">
+        <v>493</v>
+      </c>
+      <c r="H4" t="s">
+        <v>494</v>
+      </c>
+      <c r="I4" t="s">
+        <v>495</v>
+      </c>
       <c r="J4" t="s">
         <v>34</v>
+      </c>
+      <c r="K4" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -2209,8 +2395,23 @@
       <c r="B13" t="s">
         <v>124</v>
       </c>
+      <c r="C13" t="s">
+        <v>497</v>
+      </c>
       <c r="D13" t="s">
         <v>125</v>
+      </c>
+      <c r="E13" t="s">
+        <v>498</v>
+      </c>
+      <c r="F13" t="s">
+        <v>499</v>
+      </c>
+      <c r="G13" t="s">
+        <v>500</v>
+      </c>
+      <c r="H13" t="s">
+        <v>501</v>
       </c>
       <c r="I13" t="s">
         <v>126</v>
@@ -2404,8 +2605,32 @@
       <c r="B19" t="s">
         <v>185</v>
       </c>
+      <c r="C19" t="s">
+        <v>502</v>
+      </c>
+      <c r="D19" t="s">
+        <v>503</v>
+      </c>
+      <c r="E19" t="s">
+        <v>498</v>
+      </c>
+      <c r="F19" t="s">
+        <v>504</v>
+      </c>
+      <c r="G19" t="s">
+        <v>500</v>
+      </c>
+      <c r="H19" t="s">
+        <v>505</v>
+      </c>
+      <c r="I19" t="s">
+        <v>506</v>
+      </c>
       <c r="J19" t="s">
         <v>186</v>
+      </c>
+      <c r="K19" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -2730,8 +2955,32 @@
       <c r="B29" t="s">
         <v>287</v>
       </c>
+      <c r="C29" t="s">
+        <v>508</v>
+      </c>
+      <c r="D29" t="s">
+        <v>509</v>
+      </c>
+      <c r="E29" t="s">
+        <v>491</v>
+      </c>
+      <c r="F29" t="s">
+        <v>510</v>
+      </c>
+      <c r="G29" t="s">
+        <v>511</v>
+      </c>
+      <c r="H29" t="s">
+        <v>512</v>
+      </c>
+      <c r="I29" t="s">
+        <v>513</v>
+      </c>
       <c r="J29" t="s">
         <v>288</v>
+      </c>
+      <c r="K29" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
@@ -2846,8 +3095,32 @@
       <c r="B33" t="s">
         <v>323</v>
       </c>
+      <c r="C33" t="s">
+        <v>515</v>
+      </c>
+      <c r="D33" t="s">
+        <v>516</v>
+      </c>
+      <c r="E33" t="s">
+        <v>491</v>
+      </c>
+      <c r="F33" t="s">
+        <v>517</v>
+      </c>
+      <c r="G33" t="s">
+        <v>511</v>
+      </c>
+      <c r="H33" t="s">
+        <v>518</v>
+      </c>
+      <c r="I33" t="s">
+        <v>519</v>
+      </c>
       <c r="J33" t="s">
         <v>324</v>
+      </c>
+      <c r="K33" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
@@ -2997,8 +3270,32 @@
       <c r="B38" t="s">
         <v>370</v>
       </c>
+      <c r="C38" t="s">
+        <v>521</v>
+      </c>
+      <c r="D38" t="s">
+        <v>522</v>
+      </c>
+      <c r="E38" t="s">
+        <v>523</v>
+      </c>
+      <c r="F38" t="s">
+        <v>524</v>
+      </c>
+      <c r="G38" t="s">
+        <v>525</v>
+      </c>
+      <c r="H38" t="s">
+        <v>526</v>
+      </c>
+      <c r="I38" t="s">
+        <v>527</v>
+      </c>
       <c r="J38" t="s">
         <v>371</v>
+      </c>
+      <c r="K38" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
@@ -3078,8 +3375,32 @@
       <c r="B41" t="s">
         <v>395</v>
       </c>
+      <c r="C41" t="s">
+        <v>529</v>
+      </c>
+      <c r="D41" t="s">
+        <v>530</v>
+      </c>
+      <c r="E41" t="s">
+        <v>523</v>
+      </c>
+      <c r="F41" t="s">
+        <v>531</v>
+      </c>
+      <c r="G41" t="s">
+        <v>525</v>
+      </c>
+      <c r="H41" t="s">
+        <v>532</v>
+      </c>
+      <c r="I41" t="s">
+        <v>533</v>
+      </c>
       <c r="J41" t="s">
         <v>396</v>
+      </c>
+      <c r="K41" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
@@ -3334,8 +3655,32 @@
       <c r="B49" t="s">
         <v>475</v>
       </c>
+      <c r="C49" t="s">
+        <v>535</v>
+      </c>
+      <c r="D49" t="s">
+        <v>536</v>
+      </c>
+      <c r="E49" t="s">
+        <v>491</v>
+      </c>
+      <c r="F49" t="s">
+        <v>537</v>
+      </c>
+      <c r="G49" t="s">
+        <v>511</v>
+      </c>
+      <c r="H49" t="s">
+        <v>538</v>
+      </c>
+      <c r="I49" t="s">
+        <v>539</v>
+      </c>
       <c r="J49" t="s">
         <v>476</v>
+      </c>
+      <c r="K49" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
